--- a/test_scenarios.xlsx
+++ b/test_scenarios.xlsx
@@ -58,32 +58,8 @@
     <t xml:space="preserve">login with correct credential</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">1. open application URL(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">https://automationexercise.com/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">)
+    <t xml:space="preserve">1. open application URL(https://automationexercise.com/)
 2. should have existing account credentials</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">1. click on Signup/Login Button
@@ -92,32 +68,8 @@
 4. click on Login</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Email – </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">a1234@gmail.com
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Pass – a1234</t>
-    </r>
+    <t xml:space="preserve">Email – a1234@gmail.com
+Pass – a1234</t>
   </si>
   <si>
     <t xml:space="preserve">p1</t>
@@ -138,31 +90,7 @@
     <t xml:space="preserve">signup with all mandatory fields only</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">1.open application URL(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">https://automationexercise.com/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">1.open application URL(https://automationexercise.com/)</t>
   </si>
   <si>
     <t xml:space="preserve">1. click on Signup/Login Button
@@ -199,6 +127,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -228,6 +157,7 @@
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -240,7 +170,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="-0.25"/>
-        <bgColor rgb="FF666699"/>
+        <bgColor rgb="FF808080"/>
       </patternFill>
     </fill>
   </fills>
@@ -291,28 +221,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -338,7 +272,7 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF977500"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFC0C0C0"/>
@@ -381,7 +315,7 @@
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF2F5597"/>
+      <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
@@ -504,9 +438,9 @@
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="23.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="37.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="22.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="17.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="45.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="29.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="21.43"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -552,13 +486,13 @@
       <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -579,13 +513,13 @@
       <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -598,7 +532,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
         <v>18</v>
       </c>
@@ -608,10 +542,10 @@
       <c r="C5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>22</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -621,15 +555,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
       <c r="C6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -645,12 +579,12 @@
     <mergeCell ref="A5:A6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="https://automationexercise.com/"/>
-    <hyperlink ref="F2" r:id="rId2" display="a1234@gmail.com"/>
-    <hyperlink ref="D3" r:id="rId3" display="https://automationexercise.com/"/>
-    <hyperlink ref="F3" r:id="rId4" display="a1234@gmail.com"/>
-    <hyperlink ref="D5" r:id="rId5" display="https://automationexercise.com/"/>
-    <hyperlink ref="D6" r:id="rId6" display="https://automationexercise.com/"/>
+    <hyperlink ref="D2" r:id="rId1" display="1. open application URL(https://automationexercise.com/)&#10;2. should have existing account credentials"/>
+    <hyperlink ref="F2" r:id="rId2" display="Email – a1234@gmail.com&#10;Pass – a1234"/>
+    <hyperlink ref="D3" r:id="rId3" display="1. open application URL(https://automationexercise.com/)&#10;2. should have existing account credentials"/>
+    <hyperlink ref="F3" r:id="rId4" display="Email – a1234@gmail.com&#10;Pass – a1234"/>
+    <hyperlink ref="D5" r:id="rId5" display="1.open application URL(https://automationexercise.com/)"/>
+    <hyperlink ref="D6" r:id="rId6" display="1.open application URL(https://automationexercise.com/)"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/test_scenarios.xlsx
+++ b/test_scenarios.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
   <si>
     <t xml:space="preserve">Test Case ID</t>
   </si>
@@ -59,7 +59,8 @@
   </si>
   <si>
     <t xml:space="preserve">1. open application URL(https://automationexercise.com/)
-2. should have existing account credentials</t>
+2. should have existing account credentials
+</t>
   </si>
   <si>
     <t xml:space="preserve">1. click on Signup/Login Button
@@ -79,6 +80,10 @@
   </si>
   <si>
     <t xml:space="preserve">Login with wrong credential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. open application URL(https://automationexercise.com/)
+2. should have existing account credentials</t>
   </si>
   <si>
     <t xml:space="preserve">TC_2</t>
@@ -113,6 +118,44 @@
 4. click on signup
 - then land on signup page
 5. fill all  fields for account info</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.open application URL(https://automationexercise.com/) 2. login succssfully(pre-requisit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+1. If logged in successfully, logout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PASS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">search product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. click on Products
+2. type product name 
+3. click on search button
+4. check searched properly  
+5. check product name present</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2</t>
   </si>
 </sst>
 </file>
@@ -122,7 +165,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -158,6 +201,11 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -221,7 +269,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -246,7 +294,23 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -433,12 +497,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="23.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="45.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="40.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="29.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="21.43"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="1" width="11.53"/>
@@ -505,7 +569,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4"/>
       <c r="B3" s="1" t="s">
         <v>10</v>
@@ -514,7 +578,7 @@
         <v>17</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
@@ -532,51 +596,130 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="6" t="s">
         <v>22</v>
       </c>
+      <c r="E5" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="F5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="H5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="6" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4"/>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="C6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="H6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" s="8" customFormat="true" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="8" s="9" customFormat="true" ht="54.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" s="8" customFormat="true" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="A2:A3"/>
+    <mergeCell ref="4:4"/>
     <mergeCell ref="A5:A6"/>
+    <mergeCell ref="7:7"/>
+    <mergeCell ref="9:9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" display="1. open application URL(https://automationexercise.com/)&#10;2. should have existing account credentials"/>
@@ -585,6 +728,8 @@
     <hyperlink ref="F3" r:id="rId4" display="Email – a1234@gmail.com&#10;Pass – a1234"/>
     <hyperlink ref="D5" r:id="rId5" display="1.open application URL(https://automationexercise.com/)"/>
     <hyperlink ref="D6" r:id="rId6" display="1.open application URL(https://automationexercise.com/)"/>
+    <hyperlink ref="D8" r:id="rId7" display="1.open application URL(https://automationexercise.com/)"/>
+    <hyperlink ref="D10" r:id="rId8" display="1.open application URL(https://automationexercise.com/)"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/test_scenarios.xlsx
+++ b/test_scenarios.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Login" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="TEST_CASES" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="47">
   <si>
     <t xml:space="preserve">Test Case ID</t>
   </si>
@@ -151,11 +151,46 @@
     <t xml:space="preserve">1. click on Products
 2. type product name 
 3. click on search button
-4. check searched properly  
-5. check product name present</t>
+4. check searched properly  based on assert</t>
   </si>
   <si>
     <t xml:space="preserve">P2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">search product then view product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. click on Products
+2. type product name 
+3. click on search button
+4. check searched properly  based on assert
+5. click on specific product’s view product
+6. validate if landed to product details page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">product details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">submit review of product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.open application URL(https://automationexercise.com/)
+2. land to specific product details page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.TC_5 test case should be completed
+2. so once landed to product details page, fill details
+3. submit
+4. validate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P3</t>
   </si>
 </sst>
 </file>
@@ -165,7 +200,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -204,6 +239,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -269,7 +310,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -311,6 +352,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -497,12 +542,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="23.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="40.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="51.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="29.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="21.43"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="1" width="11.53"/>
@@ -685,7 +731,7 @@
     </row>
     <row r="9" s="8" customFormat="true" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="9" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -713,13 +759,67 @@
         <v>16</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="81.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="4:4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="7:7"/>
     <mergeCell ref="9:9"/>
+    <mergeCell ref="12:12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" display="1. open application URL(https://automationexercise.com/)&#10;2. should have existing account credentials"/>
@@ -730,6 +830,7 @@
     <hyperlink ref="D6" r:id="rId6" display="1.open application URL(https://automationexercise.com/)"/>
     <hyperlink ref="D8" r:id="rId7" display="1.open application URL(https://automationexercise.com/)"/>
     <hyperlink ref="D10" r:id="rId8" display="1.open application URL(https://automationexercise.com/)"/>
+    <hyperlink ref="D13" r:id="rId9" display="https://automationexercise.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
